--- a/PKSim/Analog13_PKSim.xlsx
+++ b/PKSim/Analog13_PKSim.xlsx
@@ -6,7 +6,7 @@
     <workbookView tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Analog13_PKSim" sheetId="1" r:id="rId3"/>
+    <sheet name="Analog14_PKSim" sheetId="1" r:id="rId3"/>
     <sheet name="Global PK-Analyses" sheetId="2" r:id="rId4"/>
     <sheet name="PK-Analyses" sheetId="3" r:id="rId5"/>
   </sheets>
@@ -19,16 +19,16 @@
     <t xml:space="preserve">Time [h]</t>
   </si>
   <si>
-    <t xml:space="preserve">Analog13-Peripheral Venous Blood-Plasma-Concentration [µmol/l]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog13-Arterial Blood-Plasma-Concentration [µmol/l]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog13-Brain-Tissue-Concentration [µmol/l]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog13-Liver-Tissue-Concentration [µmol/l]</t>
+    <t xml:space="preserve">Analog14-Peripheral Venous Blood-Plasma-Concentration [µmol/l]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog14-Arterial Blood-Plasma-Concentration [µmol/l]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog14-Brain-Tissue-Concentration [µmol/l]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog14-Liver-Tissue-Concentration [µmol/l]</t>
   </si>
   <si>
     <t xml:space="preserve">Parameter</t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Vss (plasma)</t>
   </si>
   <si>
-    <t xml:space="preserve">Analog13</t>
+    <t xml:space="preserve">Analog14</t>
   </si>
   <si>
     <t xml:space="preserve">ml/kg</t>
@@ -64,16 +64,16 @@
     <t xml:space="preserve">Vss (phys-chem)</t>
   </si>
   <si>
-    <t xml:space="preserve">Analog13 - Analog13-Arterial Blood-Plasma-Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog13 - Analog13-Brain-Tissue-Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog13 - Analog13-Liver-Tissue-Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog13 - Analog13-Peripheral Venous Blood-Plasma-Concentration</t>
+    <t xml:space="preserve">Analog14 - Analog14-Arterial Blood-Plasma-Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog14 - Analog14-Brain-Tissue-Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog14 - Analog14-Liver-Tissue-Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog14 - Analog14-Peripheral Venous Blood-Plasma-Concentration</t>
   </si>
   <si>
     <t xml:space="preserve">AUC_inf [µmol*min/l]</t>
@@ -218,16 +218,16 @@
         <v>0.05</v>
       </c>
       <c r="B3" s="2">
-        <v>0.001492305</v>
+        <v>0.001477058</v>
       </c>
       <c r="C3" s="2">
-        <v>0.001145137</v>
+        <v>0.001132421</v>
       </c>
       <c r="D3" s="2">
-        <v>3.198833E-06</v>
+        <v>3.042318E-06</v>
       </c>
       <c r="E3" s="2">
-        <v>0.001728543</v>
+        <v>0.00166701</v>
       </c>
     </row>
     <row r="4">
@@ -235,16 +235,16 @@
         <v>0.1</v>
       </c>
       <c r="B4" s="2">
-        <v>0.0009697333</v>
+        <v>0.0009597698</v>
       </c>
       <c r="C4" s="2">
-        <v>0.0008144132</v>
+        <v>0.0007917332</v>
       </c>
       <c r="D4" s="2">
-        <v>2.789094E-06</v>
+        <v>2.49758E-06</v>
       </c>
       <c r="E4" s="2">
-        <v>0.002096122</v>
+        <v>0.002076534</v>
       </c>
     </row>
     <row r="5">
@@ -252,16 +252,16 @@
         <v>0.15</v>
       </c>
       <c r="B5" s="2">
-        <v>0.0007466042</v>
+        <v>0.0007289672</v>
       </c>
       <c r="C5" s="2">
-        <v>0.0007126728</v>
+        <v>0.0006863893</v>
       </c>
       <c r="D5" s="2">
-        <v>2.895342E-06</v>
+        <v>2.539106E-06</v>
       </c>
       <c r="E5" s="2">
-        <v>0.00200271</v>
+        <v>0.002028613</v>
       </c>
     </row>
     <row r="6">
@@ -269,16 +269,16 @@
         <v>0.2</v>
       </c>
       <c r="B6" s="2">
-        <v>0.0006425599</v>
+        <v>0.0006221705</v>
       </c>
       <c r="C6" s="2">
-        <v>0.0006429041</v>
+        <v>0.0006197701</v>
       </c>
       <c r="D6" s="2">
-        <v>3.037338E-06</v>
+        <v>2.637972E-06</v>
       </c>
       <c r="E6" s="2">
-        <v>0.001806102</v>
+        <v>0.001858013</v>
       </c>
     </row>
     <row r="7">
@@ -286,16 +286,16 @@
         <v>0.25</v>
       </c>
       <c r="B7" s="2">
-        <v>0.0005795247</v>
+        <v>0.0005597439</v>
       </c>
       <c r="C7" s="2">
-        <v>0.0005846355</v>
+        <v>0.0005654285</v>
       </c>
       <c r="D7" s="2">
-        <v>3.174989E-06</v>
+        <v>2.7401E-06</v>
       </c>
       <c r="E7" s="2">
-        <v>0.001609794</v>
+        <v>0.001672906</v>
       </c>
     </row>
     <row r="8">
@@ -303,16 +303,16 @@
         <v>0.3</v>
       </c>
       <c r="B8" s="2">
-        <v>0.0005328284</v>
+        <v>0.0005145475</v>
       </c>
       <c r="C8" s="2">
-        <v>0.0005350732</v>
+        <v>0.0005188822</v>
       </c>
       <c r="D8" s="2">
-        <v>3.305992E-06</v>
+        <v>2.838711E-06</v>
       </c>
       <c r="E8" s="2">
-        <v>0.001438506</v>
+        <v>0.001504487</v>
       </c>
     </row>
     <row r="9">
@@ -320,16 +320,16 @@
         <v>0.35</v>
       </c>
       <c r="B9" s="2">
-        <v>0.0004948176</v>
+        <v>0.0004778703</v>
       </c>
       <c r="C9" s="2">
-        <v>0.0004930274</v>
+        <v>0.0004788306</v>
       </c>
       <c r="D9" s="2">
-        <v>3.431463E-06</v>
+        <v>2.93364E-06</v>
       </c>
       <c r="E9" s="2">
-        <v>0.001294567</v>
+        <v>0.001359192</v>
       </c>
     </row>
     <row r="10">
@@ -337,16 +337,16 @@
         <v>0.4</v>
       </c>
       <c r="B10" s="2">
-        <v>0.0004627688</v>
+        <v>0.0004467666</v>
       </c>
       <c r="C10" s="2">
-        <v>0.0004573475</v>
+        <v>0.0004443843</v>
       </c>
       <c r="D10" s="2">
-        <v>3.552257E-06</v>
+        <v>3.025413E-06</v>
       </c>
       <c r="E10" s="2">
-        <v>0.001174575</v>
+        <v>0.001235793</v>
       </c>
     </row>
     <row r="11">
@@ -354,16 +354,16 @@
         <v>0.45</v>
       </c>
       <c r="B11" s="2">
-        <v>0.0004353377</v>
+        <v>0.0004199402</v>
       </c>
       <c r="C11" s="2">
-        <v>0.0004269511</v>
+        <v>0.0004147062</v>
       </c>
       <c r="D11" s="2">
-        <v>3.668903E-06</v>
+        <v>3.114402E-06</v>
       </c>
       <c r="E11" s="2">
-        <v>0.001074327</v>
+        <v>0.001131215</v>
       </c>
     </row>
     <row r="12">
@@ -371,16 +371,16 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="2">
-        <v>0.0004116269</v>
+        <v>0.0003966052</v>
       </c>
       <c r="C12" s="2">
-        <v>0.0004008946</v>
+        <v>0.0003890361</v>
       </c>
       <c r="D12" s="2">
-        <v>3.781741E-06</v>
+        <v>3.200833E-06</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0009901022</v>
+        <v>0.001042318</v>
       </c>
     </row>
     <row r="13">
@@ -388,16 +388,16 @@
         <v>0.55</v>
       </c>
       <c r="B13" s="2">
-        <v>0.0003909597</v>
+        <v>0.0003761691</v>
       </c>
       <c r="C13" s="2">
-        <v>0.0003784052</v>
+        <v>0.0003667233</v>
       </c>
       <c r="D13" s="2">
-        <v>3.891055E-06</v>
+        <v>3.284869E-06</v>
       </c>
       <c r="E13" s="2">
-        <v>0.0009188477</v>
+        <v>0.0009663812</v>
       </c>
     </row>
     <row r="14">
@@ -405,16 +405,16 @@
         <v>0.6</v>
       </c>
       <c r="B14" s="2">
-        <v>0.0003728039</v>
+        <v>0.0003581668</v>
       </c>
       <c r="C14" s="2">
-        <v>0.0003588515</v>
+        <v>0.0003472236</v>
       </c>
       <c r="D14" s="2">
-        <v>3.997079E-06</v>
+        <v>3.366648E-06</v>
       </c>
       <c r="E14" s="2">
-        <v>0.0008581201</v>
+        <v>0.0009011367</v>
       </c>
     </row>
     <row r="15">
@@ -422,16 +422,16 @@
         <v>0.65</v>
       </c>
       <c r="B15" s="2">
-        <v>0.000356722</v>
+        <v>0.0003422061</v>
       </c>
       <c r="C15" s="2">
-        <v>0.0003417221</v>
+        <v>0.000330082</v>
       </c>
       <c r="D15" s="2">
-        <v>4.100018E-06</v>
+        <v>3.446282E-06</v>
       </c>
       <c r="E15" s="2">
-        <v>0.0008059929</v>
+        <v>0.0008447571</v>
       </c>
     </row>
     <row r="16">
@@ -439,16 +439,16 @@
         <v>0.7</v>
       </c>
       <c r="B16" s="2">
-        <v>0.0003423597</v>
+        <v>0.0003279607</v>
       </c>
       <c r="C16" s="2">
-        <v>0.0003266037</v>
+        <v>0.0003149245</v>
       </c>
       <c r="D16" s="2">
-        <v>4.200059E-06</v>
+        <v>3.523878E-06</v>
       </c>
       <c r="E16" s="2">
-        <v>0.0007609304</v>
+        <v>0.000795765</v>
       </c>
     </row>
     <row r="17">
@@ -456,16 +456,16 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="2">
-        <v>0.0003294384</v>
+        <v>0.0003151671</v>
       </c>
       <c r="C17" s="2">
-        <v>0.0003131629</v>
+        <v>0.0003014437</v>
       </c>
       <c r="D17" s="2">
-        <v>4.297374E-06</v>
+        <v>3.599542E-06</v>
       </c>
       <c r="E17" s="2">
-        <v>0.0007216872</v>
+        <v>0.0007529466</v>
       </c>
     </row>
     <row r="18">
@@ -473,16 +473,16 @@
         <v>0.8</v>
       </c>
       <c r="B18" s="2">
-        <v>0.0003177329</v>
+        <v>0.0003036106</v>
       </c>
       <c r="C18" s="2">
-        <v>0.0003011278</v>
+        <v>0.0002893847</v>
       </c>
       <c r="D18" s="2">
-        <v>4.392118E-06</v>
+        <v>3.673369E-06</v>
       </c>
       <c r="E18" s="2">
-        <v>0.0006872606</v>
+        <v>0.0007153042</v>
       </c>
     </row>
     <row r="19">
@@ -490,16 +490,16 @@
         <v>0.85</v>
       </c>
       <c r="B19" s="2">
-        <v>0.0003070547</v>
+        <v>0.0002931094</v>
       </c>
       <c r="C19" s="2">
-        <v>0.0002902754</v>
+        <v>0.000278535</v>
       </c>
       <c r="D19" s="2">
-        <v>4.484427E-06</v>
+        <v>3.745446E-06</v>
       </c>
       <c r="E19" s="2">
-        <v>0.0006568476</v>
+        <v>0.0006820247</v>
       </c>
     </row>
     <row r="20">
@@ -507,16 +507,16 @@
         <v>0.9</v>
       </c>
       <c r="B20" s="2">
-        <v>0.0002972497</v>
+        <v>0.0002835108</v>
       </c>
       <c r="C20" s="2">
-        <v>0.0002804237</v>
+        <v>0.0002687178</v>
       </c>
       <c r="D20" s="2">
-        <v>4.574426E-06</v>
+        <v>3.815854E-06</v>
       </c>
       <c r="E20" s="2">
-        <v>0.0006297934</v>
+        <v>0.0006524401</v>
       </c>
     </row>
     <row r="21">
@@ -524,16 +524,16 @@
         <v>0.95</v>
       </c>
       <c r="B21" s="2">
-        <v>0.0002881939</v>
+        <v>0.0002746901</v>
       </c>
       <c r="C21" s="2">
-        <v>0.0002714232</v>
+        <v>0.0002597861</v>
       </c>
       <c r="D21" s="2">
-        <v>4.662229E-06</v>
+        <v>3.884669E-06</v>
       </c>
       <c r="E21" s="2">
-        <v>0.000605558</v>
+        <v>0.0006259917</v>
       </c>
     </row>
     <row r="22">
@@ -541,16 +541,16 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>0.0002797848</v>
+        <v>0.0002665436</v>
       </c>
       <c r="C22" s="2">
-        <v>0.0002631503</v>
+        <v>0.0002516166</v>
       </c>
       <c r="D22" s="2">
-        <v>4.747941E-06</v>
+        <v>3.951961E-06</v>
       </c>
       <c r="E22" s="2">
-        <v>0.0005836992</v>
+        <v>0.0006022133</v>
       </c>
     </row>
     <row r="23">
@@ -558,16 +558,16 @@
         <v>1.05</v>
       </c>
       <c r="B23" s="2">
-        <v>0.0002719369</v>
+        <v>0.0002589834</v>
       </c>
       <c r="C23" s="2">
-        <v>0.0002555028</v>
+        <v>0.0002441055</v>
       </c>
       <c r="D23" s="2">
-        <v>4.831653E-06</v>
+        <v>4.017795E-06</v>
       </c>
       <c r="E23" s="2">
-        <v>0.0005638556</v>
+        <v>0.0005807176</v>
       </c>
     </row>
     <row r="24">
@@ -575,16 +575,16 @@
         <v>1.1</v>
       </c>
       <c r="B24" s="2">
-        <v>0.0002645788</v>
+        <v>0.0002519348</v>
       </c>
       <c r="C24" s="2">
-        <v>0.0002483962</v>
+        <v>0.0002371654</v>
       </c>
       <c r="D24" s="2">
-        <v>4.913454E-06</v>
+        <v>4.082229E-06</v>
       </c>
       <c r="E24" s="2">
-        <v>0.0005457292</v>
+        <v>0.0005611816</v>
       </c>
     </row>
     <row r="25">
@@ -592,16 +592,16 @@
         <v>1.15</v>
       </c>
       <c r="B25" s="2">
-        <v>0.0002576515</v>
+        <v>0.0002453344</v>
       </c>
       <c r="C25" s="2">
-        <v>0.0002417601</v>
+        <v>0.0002307225</v>
       </c>
       <c r="D25" s="2">
-        <v>4.993422E-06</v>
+        <v>4.145319E-06</v>
       </c>
       <c r="E25" s="2">
-        <v>0.0005290725</v>
+        <v>0.0005433325</v>
       </c>
     </row>
     <row r="26">
@@ -609,16 +609,16 @@
         <v>1.2</v>
       </c>
       <c r="B26" s="2">
-        <v>0.0002511058</v>
+        <v>0.00023913</v>
       </c>
       <c r="C26" s="2">
-        <v>0.000235536</v>
+        <v>0.0002247146</v>
       </c>
       <c r="D26" s="2">
-        <v>5.071631E-06</v>
+        <v>4.207116E-06</v>
       </c>
       <c r="E26" s="2">
-        <v>0.0005136802</v>
+        <v>0.0005269397</v>
       </c>
     </row>
     <row r="27">
@@ -626,16 +626,16 @@
         <v>1.25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.0002448996</v>
+        <v>0.0002332772</v>
       </c>
       <c r="C27" s="2">
-        <v>0.000229674</v>
+        <v>0.0002190891</v>
       </c>
       <c r="D27" s="2">
-        <v>5.148151E-06</v>
+        <v>4.267667E-06</v>
       </c>
       <c r="E27" s="2">
-        <v>0.0004993797</v>
+        <v>0.0005118092</v>
       </c>
     </row>
     <row r="28">
@@ -643,16 +643,16 @@
         <v>1.3</v>
       </c>
       <c r="B28" s="2">
-        <v>0.0002389988</v>
+        <v>0.0002277381</v>
       </c>
       <c r="C28" s="2">
-        <v>0.0002241332</v>
+        <v>0.0002138014</v>
       </c>
       <c r="D28" s="2">
-        <v>5.223043E-06</v>
+        <v>4.32702E-06</v>
       </c>
       <c r="E28" s="2">
-        <v>0.0004860287</v>
+        <v>0.0004977776</v>
       </c>
     </row>
     <row r="29">
@@ -660,16 +660,16 @@
         <v>1.35</v>
       </c>
       <c r="B29" s="2">
-        <v>0.000233374</v>
+        <v>0.0002224802</v>
       </c>
       <c r="C29" s="2">
-        <v>0.0002188791</v>
+        <v>0.0002088135</v>
       </c>
       <c r="D29" s="2">
-        <v>5.296369E-06</v>
+        <v>4.385214E-06</v>
       </c>
       <c r="E29" s="2">
-        <v>0.0004735092</v>
+        <v>0.0004847074</v>
       </c>
     </row>
     <row r="30">
@@ -677,16 +677,16 @@
         <v>1.4</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0002280003</v>
+        <v>0.0002174757</v>
       </c>
       <c r="C30" s="2">
-        <v>0.0002138826</v>
+        <v>0.0002040931</v>
       </c>
       <c r="D30" s="2">
-        <v>5.368185E-06</v>
+        <v>4.44229E-06</v>
       </c>
       <c r="E30" s="2">
-        <v>0.0004617228</v>
+        <v>0.0004724826</v>
       </c>
     </row>
     <row r="31">
@@ -694,16 +694,16 @@
         <v>1.45</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0002228563</v>
+        <v>0.0002127009</v>
       </c>
       <c r="C31" s="2">
-        <v>0.0002091193</v>
+        <v>0.0001996127</v>
       </c>
       <c r="D31" s="2">
-        <v>5.438543E-06</v>
+        <v>4.498284E-06</v>
       </c>
       <c r="E31" s="2">
-        <v>0.0004505875</v>
+        <v>0.0004610045</v>
       </c>
     </row>
     <row r="32">
@@ -711,16 +711,16 @@
         <v>1.5</v>
       </c>
       <c r="B32" s="2">
-        <v>0.0002179238</v>
+        <v>0.0002081349</v>
       </c>
       <c r="C32" s="2">
-        <v>0.0002045682</v>
+        <v>0.0001953486</v>
       </c>
       <c r="D32" s="2">
-        <v>5.507494E-06</v>
+        <v>4.553233E-06</v>
       </c>
       <c r="E32" s="2">
-        <v>0.0004400332</v>
+        <v>0.0004501883</v>
       </c>
     </row>
     <row r="33">
@@ -728,16 +728,16 @@
         <v>1.55</v>
       </c>
       <c r="B33" s="2">
-        <v>0.0002131869</v>
+        <v>0.0002037605</v>
       </c>
       <c r="C33" s="2">
-        <v>0.0002002113</v>
+        <v>0.0001912805</v>
       </c>
       <c r="D33" s="2">
-        <v>5.575085E-06</v>
+        <v>4.60717E-06</v>
       </c>
       <c r="E33" s="2">
-        <v>0.0004300011</v>
+        <v>0.0004399623</v>
       </c>
     </row>
     <row r="34">
@@ -745,16 +745,16 @@
         <v>1.6</v>
       </c>
       <c r="B34" s="2">
-        <v>0.0002086318</v>
+        <v>0.0001995615</v>
       </c>
       <c r="C34" s="2">
-        <v>0.0001960332</v>
+        <v>0.0001873904</v>
       </c>
       <c r="D34" s="2">
-        <v>5.641363E-06</v>
+        <v>4.660127E-06</v>
       </c>
       <c r="E34" s="2">
-        <v>0.0004204403</v>
+        <v>0.0004302629</v>
       </c>
     </row>
     <row r="35">
@@ -762,16 +762,16 @@
         <v>1.65</v>
       </c>
       <c r="B35" s="2">
-        <v>0.0002042462</v>
+        <v>0.0001955252</v>
       </c>
       <c r="C35" s="2">
-        <v>0.0001920199</v>
+        <v>0.0001836634</v>
       </c>
       <c r="D35" s="2">
-        <v>5.70637E-06</v>
+        <v>4.712135E-06</v>
       </c>
       <c r="E35" s="2">
-        <v>0.0004113066</v>
+        <v>0.0004210381</v>
       </c>
     </row>
     <row r="36">
@@ -779,16 +779,16 @@
         <v>1.7</v>
       </c>
       <c r="B36" s="2">
-        <v>0.00020002</v>
+        <v>0.0001916394</v>
       </c>
       <c r="C36" s="2">
-        <v>0.0001881601</v>
+        <v>0.0001800859</v>
       </c>
       <c r="D36" s="2">
-        <v>5.770149E-06</v>
+        <v>4.763222E-06</v>
       </c>
       <c r="E36" s="2">
-        <v>0.0004025639</v>
+        <v>0.0004122408</v>
       </c>
     </row>
     <row r="37">
@@ -796,16 +796,16 @@
         <v>1.75</v>
       </c>
       <c r="B37" s="2">
-        <v>0.0001959433</v>
+        <v>0.0001878943</v>
       </c>
       <c r="C37" s="2">
-        <v>0.0001844433</v>
+        <v>0.0001766468</v>
       </c>
       <c r="D37" s="2">
-        <v>5.832738E-06</v>
+        <v>4.813417E-06</v>
       </c>
       <c r="E37" s="2">
-        <v>0.0003941789</v>
+        <v>0.0004038333</v>
       </c>
     </row>
     <row r="38">
@@ -813,16 +813,16 @@
         <v>1.8</v>
       </c>
       <c r="B38" s="2">
-        <v>0.0001920084</v>
+        <v>0.0001842809</v>
       </c>
       <c r="C38" s="2">
-        <v>0.000180861</v>
+        <v>0.0001733362</v>
       </c>
       <c r="D38" s="2">
-        <v>5.894176E-06</v>
+        <v>4.862746E-06</v>
       </c>
       <c r="E38" s="2">
-        <v>0.0003861264</v>
+        <v>0.0003957817</v>
       </c>
     </row>
     <row r="39">
@@ -830,16 +830,16 @@
         <v>1.85</v>
       </c>
       <c r="B39" s="2">
-        <v>0.0001882079</v>
+        <v>0.0001807914</v>
       </c>
       <c r="C39" s="2">
-        <v>0.0001774053</v>
+        <v>0.0001701454</v>
       </c>
       <c r="D39" s="2">
-        <v>5.9545E-06</v>
+        <v>4.911236E-06</v>
       </c>
       <c r="E39" s="2">
-        <v>0.0003783821</v>
+        <v>0.0003880577</v>
       </c>
     </row>
     <row r="40">
@@ -847,16 +847,16 @@
         <v>1.9</v>
       </c>
       <c r="B40" s="2">
-        <v>0.0001845353</v>
+        <v>0.0001774188</v>
       </c>
       <c r="C40" s="2">
-        <v>0.0001740694</v>
+        <v>0.000167067</v>
       </c>
       <c r="D40" s="2">
-        <v>6.013744E-06</v>
+        <v>4.95891E-06</v>
       </c>
       <c r="E40" s="2">
-        <v>0.000370927</v>
+        <v>0.0003806364</v>
       </c>
     </row>
     <row r="41">
@@ -864,16 +864,16 @@
         <v>1.95</v>
       </c>
       <c r="B41" s="2">
-        <v>0.0001809847</v>
+        <v>0.0001741568</v>
       </c>
       <c r="C41" s="2">
-        <v>0.0001708474</v>
+        <v>0.0001640942</v>
       </c>
       <c r="D41" s="2">
-        <v>6.071943E-06</v>
+        <v>5.005794E-06</v>
       </c>
       <c r="E41" s="2">
-        <v>0.0003637434</v>
+        <v>0.0003734959</v>
       </c>
     </row>
     <row r="42">
@@ -881,16 +881,16 @@
         <v>2</v>
       </c>
       <c r="B42" s="2">
-        <v>0.0001775509</v>
+        <v>0.0001709999</v>
       </c>
       <c r="C42" s="2">
-        <v>0.0001677337</v>
+        <v>0.000161221</v>
       </c>
       <c r="D42" s="2">
-        <v>6.129128E-06</v>
+        <v>5.051909E-06</v>
       </c>
       <c r="E42" s="2">
-        <v>0.0003568156</v>
+        <v>0.0003666172</v>
       </c>
     </row>
     <row r="43">
@@ -898,16 +898,16 @@
         <v>2.25</v>
       </c>
       <c r="B43" s="2">
-        <v>0.0001619713</v>
+        <v>0.0001566268</v>
       </c>
       <c r="C43" s="2">
-        <v>0.0001536295</v>
+        <v>0.0001481768</v>
       </c>
       <c r="D43" s="2">
-        <v>6.400927E-06</v>
+        <v>5.271713E-06</v>
       </c>
       <c r="E43" s="2">
-        <v>0.0003255786</v>
+        <v>0.0003356109</v>
       </c>
     </row>
     <row r="44">
@@ -915,16 +915,16 @@
         <v>2.5</v>
       </c>
       <c r="B44" s="2">
-        <v>0.0001486894</v>
+        <v>0.0001442748</v>
       </c>
       <c r="C44" s="2">
-        <v>0.0001416208</v>
+        <v>0.0001369988</v>
       </c>
       <c r="D44" s="2">
-        <v>6.651694E-06</v>
+        <v>5.475347E-06</v>
       </c>
       <c r="E44" s="2">
-        <v>0.0002991038</v>
+        <v>0.0003092476</v>
       </c>
     </row>
     <row r="45">
@@ -932,16 +932,16 @@
         <v>2.75</v>
       </c>
       <c r="B45" s="2">
-        <v>0.000137328</v>
+        <v>0.0001336043</v>
       </c>
       <c r="C45" s="2">
-        <v>0.00013135</v>
+        <v>0.000127354</v>
       </c>
       <c r="D45" s="2">
-        <v>6.884436E-06</v>
+        <v>5.664957E-06</v>
       </c>
       <c r="E45" s="2">
-        <v>0.0002765093</v>
+        <v>0.0002865963</v>
       </c>
     </row>
     <row r="46">
@@ -949,16 +949,16 @@
         <v>3</v>
       </c>
       <c r="B46" s="2">
-        <v>0.000127596</v>
+        <v>0.0001243581</v>
       </c>
       <c r="C46" s="2">
-        <v>0.0001225499</v>
+        <v>0.0001189986</v>
       </c>
       <c r="D46" s="2">
-        <v>7.101702E-06</v>
+        <v>5.842383E-06</v>
       </c>
       <c r="E46" s="2">
-        <v>0.0002571795</v>
+        <v>0.0002670166</v>
       </c>
     </row>
     <row r="47">
@@ -966,16 +966,16 @@
         <v>3.25</v>
       </c>
       <c r="B47" s="2">
-        <v>0.0001192483</v>
+        <v>0.0001163324</v>
       </c>
       <c r="C47" s="2">
-        <v>0.0001149972</v>
+        <v>0.0001117442</v>
       </c>
       <c r="D47" s="2">
-        <v>7.305668E-06</v>
+        <v>6.00921E-06</v>
       </c>
       <c r="E47" s="2">
-        <v>0.0002406065</v>
+        <v>0.0002500396</v>
       </c>
     </row>
     <row r="48">
@@ -983,16 +983,16 @@
         <v>3.5</v>
       </c>
       <c r="B48" s="2">
-        <v>0.0001120793</v>
+        <v>0.0001093585</v>
       </c>
       <c r="C48" s="2">
-        <v>0.0001085054</v>
+        <v>0.0001054376</v>
       </c>
       <c r="D48" s="2">
-        <v>7.498188E-06</v>
+        <v>6.166807E-06</v>
       </c>
       <c r="E48" s="2">
-        <v>0.000226372</v>
+        <v>0.000235296</v>
       </c>
     </row>
     <row r="49">
@@ -1000,16 +1000,16 @@
         <v>3.75</v>
       </c>
       <c r="B49" s="2">
-        <v>0.0001059167</v>
+        <v>0.0001032927</v>
       </c>
       <c r="C49" s="2">
-        <v>0.0001029195</v>
+        <v>9.994856E-05</v>
       </c>
       <c r="D49" s="2">
-        <v>7.680845E-06</v>
+        <v>6.316359E-06</v>
       </c>
       <c r="E49" s="2">
-        <v>0.0002141335</v>
+        <v>0.0002224746</v>
       </c>
     </row>
     <row r="50">
@@ -1017,16 +1017,16 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>0.0001006126</v>
+        <v>9.801042E-05</v>
       </c>
       <c r="C50" s="2">
-        <v>9.810627E-05</v>
+        <v>9.516418E-05</v>
       </c>
       <c r="D50" s="2">
-        <v>7.854989E-06</v>
+        <v>6.458889E-06</v>
       </c>
       <c r="E50" s="2">
-        <v>0.0002035958</v>
+        <v>0.0002113058</v>
       </c>
     </row>
     <row r="51">
@@ -1034,16 +1034,16 @@
         <v>4.25</v>
       </c>
       <c r="B51" s="2">
-        <v>9.604129E-05</v>
+        <v>9.340499E-05</v>
       </c>
       <c r="C51" s="2">
-        <v>9.395237E-05</v>
+        <v>9.098834E-05</v>
       </c>
       <c r="D51" s="2">
-        <v>8.021778E-06</v>
+        <v>6.595286E-06</v>
       </c>
       <c r="E51" s="2">
-        <v>0.0001945086</v>
+        <v>0.0002015623</v>
       </c>
     </row>
     <row r="52">
@@ -1051,16 +1051,16 @@
         <v>4.5</v>
       </c>
       <c r="B52" s="2">
-        <v>9.209588E-05</v>
+        <v>8.93859E-05</v>
       </c>
       <c r="C52" s="2">
-        <v>9.036185E-05</v>
+        <v>8.733979E-05</v>
       </c>
       <c r="D52" s="2">
-        <v>8.182199E-06</v>
+        <v>6.726317E-06</v>
       </c>
       <c r="E52" s="2">
-        <v>0.0001866608</v>
+        <v>0.0001930542</v>
       </c>
     </row>
     <row r="53">
@@ -1068,16 +1068,16 @@
         <v>4.75</v>
       </c>
       <c r="B53" s="2">
-        <v>8.868557E-05</v>
+        <v>8.587519E-05</v>
       </c>
       <c r="C53" s="2">
-        <v>8.72531E-05</v>
+        <v>8.414877E-05</v>
       </c>
       <c r="D53" s="2">
-        <v>8.337092E-06</v>
+        <v>6.852646E-06</v>
       </c>
       <c r="E53" s="2">
-        <v>0.0001798729</v>
+        <v>0.0001856193</v>
       </c>
     </row>
     <row r="54">
@@ -1085,16 +1085,16 @@
         <v>5</v>
       </c>
       <c r="B54" s="2">
-        <v>8.573265E-05</v>
+        <v>8.280487E-05</v>
       </c>
       <c r="C54" s="2">
-        <v>8.455625E-05</v>
+        <v>8.13542E-05</v>
       </c>
       <c r="D54" s="2">
-        <v>8.487177E-06</v>
+        <v>6.974847E-06</v>
       </c>
       <c r="E54" s="2">
-        <v>0.0001739908</v>
+        <v>0.0001791145</v>
       </c>
     </row>
     <row r="55">
@@ -1102,16 +1102,16 @@
         <v>5.25</v>
       </c>
       <c r="B55" s="2">
-        <v>8.317069E-05</v>
+        <v>8.011559E-05</v>
       </c>
       <c r="C55" s="2">
-        <v>8.221153E-05</v>
+        <v>7.89026E-05</v>
       </c>
       <c r="D55" s="2">
-        <v>8.633069E-06</v>
+        <v>7.093419E-06</v>
       </c>
       <c r="E55" s="2">
-        <v>0.0001688827</v>
+        <v>0.0001734136</v>
       </c>
     </row>
     <row r="56">
@@ -1119,16 +1119,16 @@
         <v>5.5</v>
       </c>
       <c r="B56" s="2">
-        <v>8.094296E-05</v>
+        <v>7.7756E-05</v>
       </c>
       <c r="C56" s="2">
-        <v>8.016795E-05</v>
+        <v>7.674772E-05</v>
       </c>
       <c r="D56" s="2">
-        <v>8.775296E-06</v>
+        <v>7.208795E-06</v>
       </c>
       <c r="E56" s="2">
-        <v>0.0001644364</v>
+        <v>0.0001684074</v>
       </c>
     </row>
     <row r="57">
@@ -1136,16 +1136,16 @@
         <v>5.75</v>
       </c>
       <c r="B57" s="2">
-        <v>7.900114E-05</v>
+        <v>7.568204E-05</v>
       </c>
       <c r="C57" s="2">
-        <v>7.838207E-05</v>
+        <v>7.484999E-05</v>
       </c>
       <c r="D57" s="2">
-        <v>8.914311E-06</v>
+        <v>7.321349E-06</v>
       </c>
       <c r="E57" s="2">
-        <v>0.0001605564</v>
+        <v>0.0001640031</v>
       </c>
     </row>
     <row r="58">
@@ -1153,16 +1153,16 @@
         <v>6</v>
       </c>
       <c r="B58" s="2">
-        <v>7.73038E-05</v>
+        <v>7.385587E-05</v>
       </c>
       <c r="C58" s="2">
-        <v>7.681669E-05</v>
+        <v>7.317546E-05</v>
       </c>
       <c r="D58" s="2">
-        <v>9.050502E-06</v>
+        <v>7.431406E-06</v>
       </c>
       <c r="E58" s="2">
-        <v>0.0001571608</v>
+        <v>0.0001601216</v>
       </c>
     </row>
     <row r="59">
@@ -1170,16 +1170,16 @@
         <v>6.25</v>
       </c>
       <c r="B59" s="2">
-        <v>7.581586E-05</v>
+        <v>7.224463E-05</v>
       </c>
       <c r="C59" s="2">
-        <v>7.544023E-05</v>
+        <v>7.169465E-05</v>
       </c>
       <c r="D59" s="2">
-        <v>9.184198E-06</v>
+        <v>7.539247E-06</v>
       </c>
       <c r="E59" s="2">
-        <v>0.0001541801</v>
+        <v>0.000156694</v>
       </c>
     </row>
     <row r="60">
@@ -1187,16 +1187,16 @@
         <v>6.5</v>
       </c>
       <c r="B60" s="2">
-        <v>7.450693E-05</v>
+        <v>7.081981E-05</v>
       </c>
       <c r="C60" s="2">
-        <v>7.422541E-05</v>
+        <v>7.038191E-05</v>
       </c>
       <c r="D60" s="2">
-        <v>9.315689E-06</v>
+        <v>7.645116E-06</v>
       </c>
       <c r="E60" s="2">
-        <v>0.0001515542</v>
+        <v>0.00015366</v>
       </c>
     </row>
     <row r="61">
@@ -1204,16 +1204,16 @@
         <v>6.75</v>
       </c>
       <c r="B61" s="2">
-        <v>7.335221E-05</v>
+        <v>6.955649E-05</v>
       </c>
       <c r="C61" s="2">
-        <v>7.314988E-05</v>
+        <v>6.92148E-05</v>
       </c>
       <c r="D61" s="2">
-        <v>9.445208E-06</v>
+        <v>7.749227E-06</v>
       </c>
       <c r="E61" s="2">
-        <v>0.0001492341</v>
+        <v>0.0001509665</v>
       </c>
     </row>
     <row r="62">
@@ -1221,16 +1221,16 @@
         <v>7</v>
       </c>
       <c r="B62" s="2">
-        <v>7.232956E-05</v>
+        <v>6.843364E-05</v>
       </c>
       <c r="C62" s="2">
-        <v>7.219377E-05</v>
+        <v>6.817444E-05</v>
       </c>
       <c r="D62" s="2">
-        <v>9.572969E-06</v>
+        <v>7.851761E-06</v>
       </c>
       <c r="E62" s="2">
-        <v>0.0001471759</v>
+        <v>0.0001485697</v>
       </c>
     </row>
     <row r="63">
@@ -1238,16 +1238,16 @@
         <v>7.25</v>
       </c>
       <c r="B63" s="2">
-        <v>7.142055E-05</v>
+        <v>6.743225E-05</v>
       </c>
       <c r="C63" s="2">
-        <v>7.134049E-05</v>
+        <v>6.724366E-05</v>
       </c>
       <c r="D63" s="2">
-        <v>9.699149E-06</v>
+        <v>7.952882E-06</v>
       </c>
       <c r="E63" s="2">
-        <v>0.0001453432</v>
+        <v>0.0001464286</v>
       </c>
     </row>
     <row r="64">
@@ -1255,16 +1255,16 @@
         <v>7.5</v>
       </c>
       <c r="B64" s="2">
-        <v>7.060891E-05</v>
+        <v>6.653668E-05</v>
       </c>
       <c r="C64" s="2">
-        <v>7.057542E-05</v>
+        <v>6.640847E-05</v>
       </c>
       <c r="D64" s="2">
-        <v>9.823905E-06</v>
+        <v>8.052728E-06</v>
       </c>
       <c r="E64" s="2">
-        <v>0.0001437038</v>
+        <v>0.000144511</v>
       </c>
     </row>
     <row r="65">
@@ -1272,16 +1272,16 @@
         <v>7.75</v>
       </c>
       <c r="B65" s="2">
-        <v>6.988104E-05</v>
+        <v>6.573297E-05</v>
       </c>
       <c r="C65" s="2">
-        <v>6.988632E-05</v>
+        <v>6.56563E-05</v>
       </c>
       <c r="D65" s="2">
-        <v>9.947371E-06</v>
+        <v>8.151422E-06</v>
       </c>
       <c r="E65" s="2">
-        <v>0.0001422307</v>
+        <v>0.0001427872</v>
       </c>
     </row>
     <row r="66">
@@ -1289,16 +1289,16 @@
         <v>8</v>
       </c>
       <c r="B66" s="2">
-        <v>6.922498E-05</v>
+        <v>6.500932E-05</v>
       </c>
       <c r="C66" s="2">
-        <v>6.926241E-05</v>
+        <v>6.497659E-05</v>
       </c>
       <c r="D66" s="2">
-        <v>1.006967E-05</v>
+        <v>8.24907E-06</v>
       </c>
       <c r="E66" s="2">
-        <v>0.0001409004</v>
+        <v>0.0001412328</v>
       </c>
     </row>
     <row r="67">
@@ -1306,16 +1306,16 @@
         <v>8.25</v>
       </c>
       <c r="B67" s="2">
-        <v>6.863087E-05</v>
+        <v>6.435542E-05</v>
       </c>
       <c r="C67" s="2">
-        <v>6.869485E-05</v>
+        <v>6.436008E-05</v>
       </c>
       <c r="D67" s="2">
-        <v>1.019089E-05</v>
+        <v>8.345762E-06</v>
       </c>
       <c r="E67" s="2">
-        <v>0.0001396932</v>
+        <v>0.0001398259</v>
       </c>
     </row>
     <row r="68">
@@ -1323,16 +1323,16 @@
         <v>8.5</v>
       </c>
       <c r="B68" s="2">
-        <v>6.809026E-05</v>
+        <v>6.376233E-05</v>
       </c>
       <c r="C68" s="2">
-        <v>6.8176E-05</v>
+        <v>6.379872E-05</v>
       </c>
       <c r="D68" s="2">
-        <v>1.031112E-05</v>
+        <v>8.44158E-06</v>
       </c>
       <c r="E68" s="2">
-        <v>0.0001385925</v>
+        <v>0.0001385479</v>
       </c>
     </row>
     <row r="69">
@@ -1340,16 +1340,16 @@
         <v>8.75</v>
       </c>
       <c r="B69" s="2">
-        <v>6.759597E-05</v>
+        <v>6.32223E-05</v>
       </c>
       <c r="C69" s="2">
-        <v>6.769943E-05</v>
+        <v>6.328552E-05</v>
       </c>
       <c r="D69" s="2">
-        <v>1.043044E-05</v>
+        <v>8.536593E-06</v>
       </c>
       <c r="E69" s="2">
-        <v>0.0001375841</v>
+        <v>0.0001373821</v>
       </c>
     </row>
     <row r="70">
@@ -1357,16 +1357,16 @@
         <v>9</v>
       </c>
       <c r="B70" s="2">
-        <v>6.714187E-05</v>
+        <v>6.272859E-05</v>
       </c>
       <c r="C70" s="2">
-        <v>6.725961E-05</v>
+        <v>6.28144E-05</v>
       </c>
       <c r="D70" s="2">
-        <v>1.054891E-05</v>
+        <v>8.630865E-06</v>
       </c>
       <c r="E70" s="2">
-        <v>0.0001366557</v>
+        <v>0.0001363143</v>
       </c>
     </row>
     <row r="71">
@@ -1374,16 +1374,16 @@
         <v>9.25</v>
       </c>
       <c r="B71" s="2">
-        <v>6.672286E-05</v>
+        <v>6.227537E-05</v>
       </c>
       <c r="C71" s="2">
-        <v>6.685191E-05</v>
+        <v>6.238012E-05</v>
       </c>
       <c r="D71" s="2">
-        <v>1.066659E-05</v>
+        <v>8.724447E-06</v>
       </c>
       <c r="E71" s="2">
-        <v>0.0001357974</v>
+        <v>0.0001353323</v>
       </c>
     </row>
     <row r="72">
@@ -1391,16 +1391,16 @@
         <v>9.5</v>
       </c>
       <c r="B72" s="2">
-        <v>6.633443E-05</v>
+        <v>6.185763E-05</v>
       </c>
       <c r="C72" s="2">
-        <v>6.647231E-05</v>
+        <v>6.19782E-05</v>
       </c>
       <c r="D72" s="2">
-        <v>1.078352E-05</v>
+        <v>8.817389E-06</v>
       </c>
       <c r="E72" s="2">
-        <v>0.0001350001</v>
+        <v>0.0001344254</v>
       </c>
     </row>
     <row r="73">
@@ -1408,16 +1408,16 @@
         <v>9.75</v>
       </c>
       <c r="B73" s="2">
-        <v>6.597229E-05</v>
+        <v>6.147102E-05</v>
       </c>
       <c r="C73" s="2">
-        <v>6.611693E-05</v>
+        <v>6.16047E-05</v>
       </c>
       <c r="D73" s="2">
-        <v>1.089976E-05</v>
+        <v>8.909733E-06</v>
       </c>
       <c r="E73" s="2">
-        <v>0.0001342555</v>
+        <v>0.0001335846</v>
       </c>
     </row>
     <row r="74">
@@ -1425,16 +1425,16 @@
         <v>10</v>
       </c>
       <c r="B74" s="2">
-        <v>6.563401E-05</v>
+        <v>6.111179E-05</v>
       </c>
       <c r="C74" s="2">
-        <v>6.578357E-05</v>
+        <v>6.125625E-05</v>
       </c>
       <c r="D74" s="2">
-        <v>1.101533E-05</v>
+        <v>9.001514E-06</v>
       </c>
       <c r="E74" s="2">
-        <v>0.0001335586</v>
+        <v>0.000132802</v>
       </c>
     </row>
     <row r="75">
@@ -1442,16 +1442,16 @@
         <v>10.25</v>
       </c>
       <c r="B75" s="2">
-        <v>6.531614E-05</v>
+        <v>6.077669E-05</v>
       </c>
       <c r="C75" s="2">
-        <v>6.546912E-05</v>
+        <v>6.092993E-05</v>
       </c>
       <c r="D75" s="2">
-        <v>1.113027E-05</v>
+        <v>9.092765E-06</v>
       </c>
       <c r="E75" s="2">
-        <v>0.0001329026</v>
+        <v>0.0001320707</v>
       </c>
     </row>
     <row r="76">
@@ -1459,16 +1459,16 @@
         <v>10.5</v>
       </c>
       <c r="B76" s="2">
-        <v>6.501545E-05</v>
+        <v>6.046288E-05</v>
       </c>
       <c r="C76" s="2">
-        <v>6.517067E-05</v>
+        <v>6.062319E-05</v>
       </c>
       <c r="D76" s="2">
-        <v>1.124461E-05</v>
+        <v>9.183515E-06</v>
       </c>
       <c r="E76" s="2">
-        <v>0.0001322812</v>
+        <v>0.0001313848</v>
       </c>
     </row>
     <row r="77">
@@ -1476,16 +1476,16 @@
         <v>10.75</v>
       </c>
       <c r="B77" s="2">
-        <v>6.473128E-05</v>
+        <v>6.016784E-05</v>
       </c>
       <c r="C77" s="2">
-        <v>6.488762E-05</v>
+        <v>6.033374E-05</v>
       </c>
       <c r="D77" s="2">
-        <v>1.135838E-05</v>
+        <v>9.273791E-06</v>
       </c>
       <c r="E77" s="2">
-        <v>0.000131693</v>
+        <v>0.0001307387</v>
       </c>
     </row>
     <row r="78">
@@ -1493,16 +1493,16 @@
         <v>11</v>
       </c>
       <c r="B78" s="2">
-        <v>6.446077E-05</v>
+        <v>5.98896E-05</v>
       </c>
       <c r="C78" s="2">
-        <v>6.461738E-05</v>
+        <v>6.00598E-05</v>
       </c>
       <c r="D78" s="2">
-        <v>1.14716E-05</v>
+        <v>9.363613E-06</v>
       </c>
       <c r="E78" s="2">
-        <v>0.0001311323</v>
+        <v>0.0001301286</v>
       </c>
     </row>
     <row r="79">
@@ -1510,16 +1510,16 @@
         <v>11.25</v>
       </c>
       <c r="B79" s="2">
-        <v>6.420197E-05</v>
+        <v>5.962609E-05</v>
       </c>
       <c r="C79" s="2">
-        <v>6.435818E-05</v>
+        <v>5.97995E-05</v>
       </c>
       <c r="D79" s="2">
-        <v>1.158431E-05</v>
+        <v>9.453003E-06</v>
       </c>
       <c r="E79" s="2">
-        <v>0.0001305953</v>
+        <v>0.0001295498</v>
       </c>
     </row>
     <row r="80">
@@ -1527,16 +1527,16 @@
         <v>11.5</v>
       </c>
       <c r="B80" s="2">
-        <v>6.395454E-05</v>
+        <v>5.937579E-05</v>
       </c>
       <c r="C80" s="2">
-        <v>6.410973E-05</v>
+        <v>5.955148E-05</v>
       </c>
       <c r="D80" s="2">
-        <v>1.16965E-05</v>
+        <v>9.54198E-06</v>
       </c>
       <c r="E80" s="2">
-        <v>0.0001300814</v>
+        <v>0.0001289992</v>
       </c>
     </row>
     <row r="81">
@@ -1544,16 +1544,16 @@
         <v>11.75</v>
       </c>
       <c r="B81" s="2">
-        <v>6.371677E-05</v>
+        <v>5.913731E-05</v>
       </c>
       <c r="C81" s="2">
-        <v>6.387047E-05</v>
+        <v>5.931448E-05</v>
       </c>
       <c r="D81" s="2">
-        <v>1.180821E-05</v>
+        <v>9.630559E-06</v>
       </c>
       <c r="E81" s="2">
-        <v>0.000129587</v>
+        <v>0.000128474</v>
       </c>
     </row>
     <row r="82">
@@ -1561,16 +1561,16 @@
         <v>12</v>
       </c>
       <c r="B82" s="2">
-        <v>6.34877E-05</v>
+        <v>5.890928E-05</v>
       </c>
       <c r="C82" s="2">
-        <v>6.363951E-05</v>
+        <v>5.908726E-05</v>
       </c>
       <c r="D82" s="2">
-        <v>1.191944E-05</v>
+        <v>9.718759E-06</v>
       </c>
       <c r="E82" s="2">
-        <v>0.0001291103</v>
+        <v>0.0001279711</v>
       </c>
     </row>
     <row r="83">
@@ -1578,16 +1578,16 @@
         <v>12.25</v>
       </c>
       <c r="B83" s="2">
-        <v>6.326679E-05</v>
+        <v>5.869081E-05</v>
       </c>
       <c r="C83" s="2">
-        <v>6.341639E-05</v>
+        <v>5.886903E-05</v>
       </c>
       <c r="D83" s="2">
-        <v>1.203021E-05</v>
+        <v>9.806588E-06</v>
       </c>
       <c r="E83" s="2">
-        <v>0.0001286503</v>
+        <v>0.0001274888</v>
       </c>
     </row>
     <row r="84">
@@ -1595,16 +1595,16 @@
         <v>12.5</v>
       </c>
       <c r="B84" s="2">
-        <v>6.305333E-05</v>
+        <v>5.848088E-05</v>
       </c>
       <c r="C84" s="2">
-        <v>6.320043E-05</v>
+        <v>5.865884E-05</v>
       </c>
       <c r="D84" s="2">
-        <v>1.214053E-05</v>
+        <v>9.89406E-06</v>
       </c>
       <c r="E84" s="2">
-        <v>0.0001282054</v>
+        <v>0.0001270249</v>
       </c>
     </row>
     <row r="85">
@@ -1612,16 +1612,16 @@
         <v>12.75</v>
       </c>
       <c r="B85" s="2">
-        <v>6.284674E-05</v>
+        <v>5.827871E-05</v>
       </c>
       <c r="C85" s="2">
-        <v>6.299112E-05</v>
+        <v>5.845601E-05</v>
       </c>
       <c r="D85" s="2">
-        <v>1.225042E-05</v>
+        <v>9.981188E-06</v>
       </c>
       <c r="E85" s="2">
-        <v>0.0001277746</v>
+        <v>0.0001265777</v>
       </c>
     </row>
     <row r="86">
@@ -1629,16 +1629,16 @@
         <v>13</v>
       </c>
       <c r="B86" s="2">
-        <v>6.264651E-05</v>
+        <v>5.808365E-05</v>
       </c>
       <c r="C86" s="2">
-        <v>6.278798E-05</v>
+        <v>5.825993E-05</v>
       </c>
       <c r="D86" s="2">
-        <v>1.235988E-05</v>
+        <v>1.006798E-05</v>
       </c>
       <c r="E86" s="2">
-        <v>0.0001273568</v>
+        <v>0.0001261459</v>
       </c>
     </row>
     <row r="87">
@@ -1646,16 +1646,16 @@
         <v>13.25</v>
       </c>
       <c r="B87" s="2">
-        <v>6.245219E-05</v>
+        <v>5.789505E-05</v>
       </c>
       <c r="C87" s="2">
-        <v>6.25906E-05</v>
+        <v>5.807003E-05</v>
       </c>
       <c r="D87" s="2">
-        <v>1.246893E-05</v>
+        <v>1.015445E-05</v>
       </c>
       <c r="E87" s="2">
-        <v>0.0001269512</v>
+        <v>0.0001257281</v>
       </c>
     </row>
     <row r="88">
@@ -1663,16 +1663,16 @@
         <v>13.5</v>
       </c>
       <c r="B88" s="2">
-        <v>6.22634E-05</v>
+        <v>5.771243E-05</v>
       </c>
       <c r="C88" s="2">
-        <v>6.239865E-05</v>
+        <v>5.788584E-05</v>
       </c>
       <c r="D88" s="2">
-        <v>1.257757E-05</v>
+        <v>1.02406E-05</v>
       </c>
       <c r="E88" s="2">
-        <v>0.000126557</v>
+        <v>0.0001253232</v>
       </c>
     </row>
     <row r="89">
@@ -1680,16 +1680,16 @@
         <v>13.75</v>
       </c>
       <c r="B89" s="2">
-        <v>6.207977E-05</v>
+        <v>5.753531E-05</v>
       </c>
       <c r="C89" s="2">
-        <v>6.221175E-05</v>
+        <v>5.770694E-05</v>
       </c>
       <c r="D89" s="2">
-        <v>1.268582E-05</v>
+        <v>1.032644E-05</v>
       </c>
       <c r="E89" s="2">
-        <v>0.0001261733</v>
+        <v>0.0001249303</v>
       </c>
     </row>
     <row r="90">
@@ -1697,16 +1697,16 @@
         <v>14</v>
       </c>
       <c r="B90" s="2">
-        <v>6.190084E-05</v>
+        <v>5.736328E-05</v>
       </c>
       <c r="C90" s="2">
-        <v>6.20295E-05</v>
+        <v>5.753296E-05</v>
       </c>
       <c r="D90" s="2">
-        <v>1.279367E-05</v>
+        <v>1.041198E-05</v>
       </c>
       <c r="E90" s="2">
-        <v>0.0001257994</v>
+        <v>0.0001245484</v>
       </c>
     </row>
     <row r="91">
@@ -1714,16 +1714,16 @@
         <v>14.25</v>
       </c>
       <c r="B91" s="2">
-        <v>6.172641E-05</v>
+        <v>5.719598E-05</v>
       </c>
       <c r="C91" s="2">
-        <v>6.185174E-05</v>
+        <v>5.736357E-05</v>
       </c>
       <c r="D91" s="2">
-        <v>1.290115E-05</v>
+        <v>1.049722E-05</v>
       </c>
       <c r="E91" s="2">
-        <v>0.0001254348</v>
+        <v>0.0001241768</v>
       </c>
     </row>
     <row r="92">
@@ -1731,16 +1731,16 @@
         <v>14.5</v>
       </c>
       <c r="B92" s="2">
-        <v>6.155621E-05</v>
+        <v>5.703307E-05</v>
       </c>
       <c r="C92" s="2">
-        <v>6.167816E-05</v>
+        <v>5.719846E-05</v>
       </c>
       <c r="D92" s="2">
-        <v>1.300826E-05</v>
+        <v>1.058217E-05</v>
       </c>
       <c r="E92" s="2">
-        <v>0.000125079</v>
+        <v>0.0001238148</v>
       </c>
     </row>
     <row r="93">
@@ -1748,16 +1748,16 @@
         <v>14.75</v>
       </c>
       <c r="B93" s="2">
-        <v>6.138988E-05</v>
+        <v>5.687431E-05</v>
       </c>
       <c r="C93" s="2">
-        <v>6.150848E-05</v>
+        <v>5.70374E-05</v>
       </c>
       <c r="D93" s="2">
-        <v>1.3115E-05</v>
+        <v>1.066685E-05</v>
       </c>
       <c r="E93" s="2">
-        <v>0.0001247312</v>
+        <v>0.0001234619</v>
       </c>
     </row>
     <row r="94">
@@ -1765,16 +1765,16 @@
         <v>15</v>
       </c>
       <c r="B94" s="2">
-        <v>6.122735E-05</v>
+        <v>5.67194E-05</v>
       </c>
       <c r="C94" s="2">
-        <v>6.134259E-05</v>
+        <v>5.688012E-05</v>
       </c>
       <c r="D94" s="2">
-        <v>1.322139E-05</v>
+        <v>1.075125E-05</v>
       </c>
       <c r="E94" s="2">
-        <v>0.0001243913</v>
+        <v>0.0001231174</v>
       </c>
     </row>
     <row r="95">
@@ -1782,16 +1782,16 @@
         <v>15.25</v>
       </c>
       <c r="B95" s="2">
-        <v>6.10684E-05</v>
+        <v>5.656815E-05</v>
       </c>
       <c r="C95" s="2">
-        <v>6.118032E-05</v>
+        <v>5.672644E-05</v>
       </c>
       <c r="D95" s="2">
-        <v>1.332743E-05</v>
+        <v>1.083537E-05</v>
       </c>
       <c r="E95" s="2">
-        <v>0.0001240589</v>
+        <v>0.0001227809</v>
       </c>
     </row>
     <row r="96">
@@ -1799,16 +1799,16 @@
         <v>15.5</v>
       </c>
       <c r="B96" s="2">
-        <v>6.091289E-05</v>
+        <v>5.642035E-05</v>
       </c>
       <c r="C96" s="2">
-        <v>6.102151E-05</v>
+        <v>5.657617E-05</v>
       </c>
       <c r="D96" s="2">
-        <v>1.343312E-05</v>
+        <v>1.091923E-05</v>
       </c>
       <c r="E96" s="2">
-        <v>0.0001237336</v>
+        <v>0.0001224521</v>
       </c>
     </row>
     <row r="97">
@@ -1816,16 +1816,16 @@
         <v>15.75</v>
       </c>
       <c r="B97" s="2">
-        <v>6.076068E-05</v>
+        <v>5.627581E-05</v>
       </c>
       <c r="C97" s="2">
-        <v>6.086604E-05</v>
+        <v>5.642914E-05</v>
       </c>
       <c r="D97" s="2">
-        <v>1.353848E-05</v>
+        <v>1.100284E-05</v>
       </c>
       <c r="E97" s="2">
-        <v>0.0001234152</v>
+        <v>0.0001221304</v>
       </c>
     </row>
     <row r="98">
@@ -1833,16 +1833,16 @@
         <v>16</v>
       </c>
       <c r="B98" s="2">
-        <v>6.061168E-05</v>
+        <v>5.613441E-05</v>
       </c>
       <c r="C98" s="2">
-        <v>6.071382E-05</v>
+        <v>5.628522E-05</v>
       </c>
       <c r="D98" s="2">
-        <v>1.364351E-05</v>
+        <v>1.108618E-05</v>
       </c>
       <c r="E98" s="2">
-        <v>0.0001231036</v>
+        <v>0.0001218156</v>
       </c>
     </row>
     <row r="99">
@@ -1850,16 +1850,16 @@
         <v>16.25</v>
       </c>
       <c r="B99" s="2">
-        <v>6.04658E-05</v>
+        <v>5.599598E-05</v>
       </c>
       <c r="C99" s="2">
-        <v>6.056476E-05</v>
+        <v>5.614427E-05</v>
       </c>
       <c r="D99" s="2">
-        <v>1.374821E-05</v>
+        <v>1.116928E-05</v>
       </c>
       <c r="E99" s="2">
-        <v>0.0001227984</v>
+        <v>0.0001215074</v>
       </c>
     </row>
     <row r="100">
@@ -1867,16 +1867,16 @@
         <v>16.5</v>
       </c>
       <c r="B100" s="2">
-        <v>6.032282E-05</v>
+        <v>5.586043E-05</v>
       </c>
       <c r="C100" s="2">
-        <v>6.041866E-05</v>
+        <v>5.600618E-05</v>
       </c>
       <c r="D100" s="2">
-        <v>1.38526E-05</v>
+        <v>1.125213E-05</v>
       </c>
       <c r="E100" s="2">
-        <v>0.0001224994</v>
+        <v>0.0001212055</v>
       </c>
     </row>
     <row r="101">
@@ -1884,16 +1884,16 @@
         <v>16.75</v>
       </c>
       <c r="B101" s="2">
-        <v>6.018274E-05</v>
+        <v>5.572762E-05</v>
       </c>
       <c r="C101" s="2">
-        <v>6.02755E-05</v>
+        <v>5.587085E-05</v>
       </c>
       <c r="D101" s="2">
-        <v>1.395667E-05</v>
+        <v>1.133474E-05</v>
       </c>
       <c r="E101" s="2">
-        <v>0.0001222064</v>
+        <v>0.0001209097</v>
       </c>
     </row>
     <row r="102">
@@ -1901,16 +1901,16 @@
         <v>17</v>
       </c>
       <c r="B102" s="2">
-        <v>6.004551E-05</v>
+        <v>5.559747E-05</v>
       </c>
       <c r="C102" s="2">
-        <v>6.013524E-05</v>
+        <v>5.573818E-05</v>
       </c>
       <c r="D102" s="2">
-        <v>1.406043E-05</v>
+        <v>1.141711E-05</v>
       </c>
       <c r="E102" s="2">
-        <v>0.0001219194</v>
+        <v>0.0001206198</v>
       </c>
     </row>
     <row r="103">
@@ -1918,16 +1918,16 @@
         <v>17.25</v>
       </c>
       <c r="B103" s="2">
-        <v>5.991106E-05</v>
+        <v>5.546986E-05</v>
       </c>
       <c r="C103" s="2">
-        <v>5.999781E-05</v>
+        <v>5.560806E-05</v>
       </c>
       <c r="D103" s="2">
-        <v>1.416388E-05</v>
+        <v>1.149924E-05</v>
       </c>
       <c r="E103" s="2">
-        <v>0.0001216381</v>
+        <v>0.0001203355</v>
       </c>
     </row>
     <row r="104">
@@ -1935,16 +1935,16 @@
         <v>17.5</v>
       </c>
       <c r="B104" s="2">
-        <v>5.977917E-05</v>
+        <v>5.534472E-05</v>
       </c>
       <c r="C104" s="2">
-        <v>5.986301E-05</v>
+        <v>5.548045E-05</v>
       </c>
       <c r="D104" s="2">
-        <v>1.426704E-05</v>
+        <v>1.158115E-05</v>
       </c>
       <c r="E104" s="2">
-        <v>0.0001213623</v>
+        <v>0.0001200567</v>
       </c>
     </row>
     <row r="105">
@@ -1952,16 +1952,16 @@
         <v>17.75</v>
       </c>
       <c r="B105" s="2">
-        <v>5.964988E-05</v>
+        <v>5.5222E-05</v>
       </c>
       <c r="C105" s="2">
-        <v>5.973086E-05</v>
+        <v>5.535526E-05</v>
       </c>
       <c r="D105" s="2">
-        <v>1.436991E-05</v>
+        <v>1.166283E-05</v>
       </c>
       <c r="E105" s="2">
-        <v>0.0001210919</v>
+        <v>0.0001197832</v>
       </c>
     </row>
     <row r="106">
@@ -1969,16 +1969,16 @@
         <v>18</v>
       </c>
       <c r="B106" s="2">
-        <v>5.952315E-05</v>
+        <v>5.510159E-05</v>
       </c>
       <c r="C106" s="2">
-        <v>5.960132E-05</v>
+        <v>5.52324E-05</v>
       </c>
       <c r="D106" s="2">
-        <v>1.447248E-05</v>
+        <v>1.174429E-05</v>
       </c>
       <c r="E106" s="2">
-        <v>0.0001208269</v>
+        <v>0.0001195149</v>
       </c>
     </row>
     <row r="107">
@@ -1986,16 +1986,16 @@
         <v>18.25</v>
       </c>
       <c r="B107" s="2">
-        <v>5.939892E-05</v>
+        <v>5.49834E-05</v>
       </c>
       <c r="C107" s="2">
-        <v>5.947433E-05</v>
+        <v>5.51118E-05</v>
       </c>
       <c r="D107" s="2">
-        <v>1.457478E-05</v>
+        <v>1.182553E-05</v>
       </c>
       <c r="E107" s="2">
-        <v>0.0001205672</v>
+        <v>0.0001192515</v>
       </c>
     </row>
     <row r="108">
@@ -2003,16 +2003,16 @@
         <v>18.5</v>
       </c>
       <c r="B108" s="2">
-        <v>5.927703E-05</v>
+        <v>5.48674E-05</v>
       </c>
       <c r="C108" s="2">
-        <v>5.934974E-05</v>
+        <v>5.499341E-05</v>
       </c>
       <c r="D108" s="2">
-        <v>1.467679E-05</v>
+        <v>1.190655E-05</v>
       </c>
       <c r="E108" s="2">
-        <v>0.0001203123</v>
+        <v>0.0001189929</v>
       </c>
     </row>
     <row r="109">
@@ -2020,16 +2020,16 @@
         <v>18.75</v>
       </c>
       <c r="B109" s="2">
-        <v>5.915748E-05</v>
+        <v>5.475355E-05</v>
       </c>
       <c r="C109" s="2">
-        <v>5.922756E-05</v>
+        <v>5.48772E-05</v>
       </c>
       <c r="D109" s="2">
-        <v>1.477853E-05</v>
+        <v>1.198737E-05</v>
       </c>
       <c r="E109" s="2">
-        <v>0.0001200624</v>
+        <v>0.0001187392</v>
       </c>
     </row>
     <row r="110">
@@ -2037,16 +2037,16 @@
         <v>19</v>
       </c>
       <c r="B110" s="2">
-        <v>5.904024E-05</v>
+        <v>5.464175E-05</v>
       </c>
       <c r="C110" s="2">
-        <v>5.910773E-05</v>
+        <v>5.476308E-05</v>
       </c>
       <c r="D110" s="2">
-        <v>1.488E-05</v>
+        <v>1.206797E-05</v>
       </c>
       <c r="E110" s="2">
-        <v>0.0001198173</v>
+        <v>0.00011849</v>
       </c>
     </row>
     <row r="111">
@@ -2054,16 +2054,16 @@
         <v>19.25</v>
       </c>
       <c r="B111" s="2">
-        <v>5.892524E-05</v>
+        <v>5.453195E-05</v>
       </c>
       <c r="C111" s="2">
-        <v>5.89902E-05</v>
+        <v>5.465099E-05</v>
       </c>
       <c r="D111" s="2">
-        <v>1.49812E-05</v>
+        <v>1.214837E-05</v>
       </c>
       <c r="E111" s="2">
-        <v>0.0001195769</v>
+        <v>0.0001182453</v>
       </c>
     </row>
     <row r="112">
@@ -2071,16 +2071,16 @@
         <v>19.5</v>
       </c>
       <c r="B112" s="2">
-        <v>5.881241E-05</v>
+        <v>5.442412E-05</v>
       </c>
       <c r="C112" s="2">
-        <v>5.887489E-05</v>
+        <v>5.454089E-05</v>
       </c>
       <c r="D112" s="2">
-        <v>1.508214E-05</v>
+        <v>1.222857E-05</v>
       </c>
       <c r="E112" s="2">
-        <v>0.0001193411</v>
+        <v>0.0001180049</v>
       </c>
     </row>
     <row r="113">
@@ -2088,16 +2088,16 @@
         <v>19.75</v>
       </c>
       <c r="B113" s="2">
-        <v>5.87017E-05</v>
+        <v>5.431821E-05</v>
       </c>
       <c r="C113" s="2">
-        <v>5.876176E-05</v>
+        <v>5.443277E-05</v>
       </c>
       <c r="D113" s="2">
-        <v>1.518282E-05</v>
+        <v>1.230857E-05</v>
       </c>
       <c r="E113" s="2">
-        <v>0.0001191097</v>
+        <v>0.0001177688</v>
       </c>
     </row>
     <row r="114">
@@ -2105,16 +2105,16 @@
         <v>20</v>
       </c>
       <c r="B114" s="2">
-        <v>5.859307E-05</v>
+        <v>5.421418E-05</v>
       </c>
       <c r="C114" s="2">
-        <v>5.865077E-05</v>
+        <v>5.432654E-05</v>
       </c>
       <c r="D114" s="2">
-        <v>1.528325E-05</v>
+        <v>1.238837E-05</v>
       </c>
       <c r="E114" s="2">
-        <v>0.0001188827</v>
+        <v>0.0001175369</v>
       </c>
     </row>
     <row r="115">
@@ -2122,16 +2122,16 @@
         <v>20.25</v>
       </c>
       <c r="B115" s="2">
-        <v>5.848648E-05</v>
+        <v>5.411197E-05</v>
       </c>
       <c r="C115" s="2">
-        <v>5.854187E-05</v>
+        <v>5.422218E-05</v>
       </c>
       <c r="D115" s="2">
-        <v>1.538343E-05</v>
+        <v>1.246798E-05</v>
       </c>
       <c r="E115" s="2">
-        <v>0.00011866</v>
+        <v>0.0001173091</v>
       </c>
     </row>
     <row r="116">
@@ -2139,16 +2139,16 @@
         <v>20.5</v>
       </c>
       <c r="B116" s="2">
-        <v>5.838188E-05</v>
+        <v>5.401156E-05</v>
       </c>
       <c r="C116" s="2">
-        <v>5.843501E-05</v>
+        <v>5.411965E-05</v>
       </c>
       <c r="D116" s="2">
-        <v>1.548337E-05</v>
+        <v>1.25474E-05</v>
       </c>
       <c r="E116" s="2">
-        <v>0.0001184415</v>
+        <v>0.0001170853</v>
       </c>
     </row>
     <row r="117">
@@ -2156,16 +2156,16 @@
         <v>20.75</v>
       </c>
       <c r="B117" s="2">
-        <v>5.827922E-05</v>
+        <v>5.391291E-05</v>
       </c>
       <c r="C117" s="2">
-        <v>5.833015E-05</v>
+        <v>5.401891E-05</v>
       </c>
       <c r="D117" s="2">
-        <v>1.558306E-05</v>
+        <v>1.262663E-05</v>
       </c>
       <c r="E117" s="2">
-        <v>0.0001182271</v>
+        <v>0.0001168654</v>
       </c>
     </row>
     <row r="118">
@@ -2173,16 +2173,16 @@
         <v>21</v>
       </c>
       <c r="B118" s="2">
-        <v>5.817847E-05</v>
+        <v>5.381598E-05</v>
       </c>
       <c r="C118" s="2">
-        <v>5.822725E-05</v>
+        <v>5.391994E-05</v>
       </c>
       <c r="D118" s="2">
-        <v>1.568251E-05</v>
+        <v>1.270568E-05</v>
       </c>
       <c r="E118" s="2">
-        <v>0.0001180166</v>
+        <v>0.0001166494</v>
       </c>
     </row>
     <row r="119">
@@ -2190,16 +2190,16 @@
         <v>21.25</v>
       </c>
       <c r="B119" s="2">
-        <v>5.807959E-05</v>
+        <v>5.372075E-05</v>
       </c>
       <c r="C119" s="2">
-        <v>5.812627E-05</v>
+        <v>5.382269E-05</v>
       </c>
       <c r="D119" s="2">
-        <v>1.578173E-05</v>
+        <v>1.278455E-05</v>
       </c>
       <c r="E119" s="2">
-        <v>0.0001178101</v>
+        <v>0.0001164371</v>
       </c>
     </row>
     <row r="120">
@@ -2207,16 +2207,16 @@
         <v>21.5</v>
       </c>
       <c r="B120" s="2">
-        <v>5.798254E-05</v>
+        <v>5.362718E-05</v>
       </c>
       <c r="C120" s="2">
-        <v>5.802717E-05</v>
+        <v>5.372713E-05</v>
       </c>
       <c r="D120" s="2">
-        <v>1.588072E-05</v>
+        <v>1.286324E-05</v>
       </c>
       <c r="E120" s="2">
-        <v>0.0001176075</v>
+        <v>0.0001162285</v>
       </c>
     </row>
     <row r="121">
@@ -2224,16 +2224,16 @@
         <v>21.75</v>
       </c>
       <c r="B121" s="2">
-        <v>5.788729E-05</v>
+        <v>5.353524E-05</v>
       </c>
       <c r="C121" s="2">
-        <v>5.792992E-05</v>
+        <v>5.363324E-05</v>
       </c>
       <c r="D121" s="2">
-        <v>1.597948E-05</v>
+        <v>1.294175E-05</v>
       </c>
       <c r="E121" s="2">
-        <v>0.0001174086</v>
+        <v>0.0001160236</v>
       </c>
     </row>
     <row r="122">
@@ -2241,16 +2241,16 @@
         <v>22</v>
       </c>
       <c r="B122" s="2">
-        <v>5.779379E-05</v>
+        <v>5.34449E-05</v>
       </c>
       <c r="C122" s="2">
-        <v>5.783447E-05</v>
+        <v>5.354097E-05</v>
       </c>
       <c r="D122" s="2">
-        <v>1.607802E-05</v>
+        <v>1.302009E-05</v>
       </c>
       <c r="E122" s="2">
-        <v>0.0001172134</v>
+        <v>0.0001158222</v>
       </c>
     </row>
     <row r="123">
@@ -2258,16 +2258,16 @@
         <v>22.25</v>
       </c>
       <c r="B123" s="2">
-        <v>5.770203E-05</v>
+        <v>5.335612E-05</v>
       </c>
       <c r="C123" s="2">
-        <v>5.77408E-05</v>
+        <v>5.345031E-05</v>
       </c>
       <c r="D123" s="2">
-        <v>1.617633E-05</v>
+        <v>1.309825E-05</v>
       </c>
       <c r="E123" s="2">
-        <v>0.0001170219</v>
+        <v>0.0001156243</v>
       </c>
     </row>
     <row r="124">
@@ -2275,16 +2275,16 @@
         <v>22.5</v>
       </c>
       <c r="B124" s="2">
-        <v>5.761195E-05</v>
+        <v>5.326888E-05</v>
       </c>
       <c r="C124" s="2">
-        <v>5.764887E-05</v>
+        <v>5.336122E-05</v>
       </c>
       <c r="D124" s="2">
-        <v>1.627443E-05</v>
+        <v>1.317625E-05</v>
       </c>
       <c r="E124" s="2">
-        <v>0.0001168339</v>
+        <v>0.0001154299</v>
       </c>
     </row>
     <row r="125">
@@ -2292,16 +2292,16 @@
         <v>22.75</v>
       </c>
       <c r="B125" s="2">
-        <v>5.752353E-05</v>
+        <v>5.318315E-05</v>
       </c>
       <c r="C125" s="2">
-        <v>5.755864E-05</v>
+        <v>5.327367E-05</v>
       </c>
       <c r="D125" s="2">
-        <v>1.637232E-05</v>
+        <v>1.325408E-05</v>
       </c>
       <c r="E125" s="2">
-        <v>0.0001166494</v>
+        <v>0.0001152388</v>
       </c>
     </row>
     <row r="126">
@@ -2309,16 +2309,16 @@
         <v>23</v>
       </c>
       <c r="B126" s="2">
-        <v>5.743674E-05</v>
+        <v>5.30989E-05</v>
       </c>
       <c r="C126" s="2">
-        <v>5.747009E-05</v>
+        <v>5.318763E-05</v>
       </c>
       <c r="D126" s="2">
-        <v>1.646999E-05</v>
+        <v>1.333175E-05</v>
       </c>
       <c r="E126" s="2">
-        <v>0.0001164683</v>
+        <v>0.000115051</v>
       </c>
     </row>
     <row r="127">
@@ -2326,16 +2326,16 @@
         <v>23.25</v>
       </c>
       <c r="B127" s="2">
-        <v>5.735156E-05</v>
+        <v>5.30161E-05</v>
       </c>
       <c r="C127" s="2">
-        <v>5.738318E-05</v>
+        <v>5.310307E-05</v>
       </c>
       <c r="D127" s="2">
-        <v>1.656746E-05</v>
+        <v>1.340926E-05</v>
       </c>
       <c r="E127" s="2">
-        <v>0.0001162906</v>
+        <v>0.0001148665</v>
       </c>
     </row>
     <row r="128">
@@ -2343,16 +2343,16 @@
         <v>23.5</v>
       </c>
       <c r="B128" s="2">
-        <v>5.726793E-05</v>
+        <v>5.293472E-05</v>
       </c>
       <c r="C128" s="2">
-        <v>5.729788E-05</v>
+        <v>5.301997E-05</v>
       </c>
       <c r="D128" s="2">
-        <v>1.666472E-05</v>
+        <v>1.34866E-05</v>
       </c>
       <c r="E128" s="2">
-        <v>0.0001161162</v>
+        <v>0.0001146851</v>
       </c>
     </row>
     <row r="129">
@@ -2360,16 +2360,16 @@
         <v>23.75</v>
       </c>
       <c r="B129" s="2">
-        <v>5.718585E-05</v>
+        <v>5.285475E-05</v>
       </c>
       <c r="C129" s="2">
-        <v>5.721416E-05</v>
+        <v>5.29383E-05</v>
       </c>
       <c r="D129" s="2">
-        <v>1.676178E-05</v>
+        <v>1.356379E-05</v>
       </c>
       <c r="E129" s="2">
-        <v>0.000115945</v>
+        <v>0.0001145069</v>
       </c>
     </row>
     <row r="130">
@@ -2377,16 +2377,16 @@
         <v>24</v>
       </c>
       <c r="B130" s="2">
-        <v>5.710527E-05</v>
+        <v>5.277614E-05</v>
       </c>
       <c r="C130" s="2">
-        <v>5.713198E-05</v>
+        <v>5.285802E-05</v>
       </c>
       <c r="D130" s="2">
-        <v>1.685864E-05</v>
+        <v>1.364083E-05</v>
       </c>
       <c r="E130" s="2">
-        <v>0.000115777</v>
+        <v>0.0001143317</v>
       </c>
     </row>
   </sheetData>
@@ -2427,7 +2427,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>4207.00073242188</v>
+        <v>4338.58919143677</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -2441,7 +2441,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>4498.58617782593</v>
+        <v>4674.57056045532</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>11</v>
@@ -2455,7 +2455,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="2">
-        <v>0.422860437538475</v>
+        <v>0.463814416434616</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -2469,7 +2469,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="2">
-        <v>7014.50959047272</v>
+        <v>7507.73803215253</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -2514,16 +2514,16 @@
         <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>0.729371428489685</v>
+        <v>0.648641705513</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>1.48114991188049</v>
+        <v>1.40726161003113</v>
       </c>
       <c r="E2" s="2">
-        <v>0.744286179542542</v>
+        <v>0.661659121513367</v>
       </c>
     </row>
     <row r="3">
@@ -2531,16 +2531,16 @@
         <v>21</v>
       </c>
       <c r="B3" s="2">
-        <v>2317457275390.63</v>
+        <v>2113617187500</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>4706109375000</v>
+        <v>4585601074218.75</v>
       </c>
       <c r="E3" s="2">
-        <v>2364846435546.88</v>
+        <v>2156034667968.75</v>
       </c>
     </row>
     <row r="4">
@@ -2548,16 +2548,16 @@
         <v>22</v>
       </c>
       <c r="B4" s="2">
-        <v>0.133127361536026</v>
+        <v>0.126150980591774</v>
       </c>
       <c r="C4" s="2">
-        <v>0.0166058577597141</v>
+        <v>0.0135353859513998</v>
       </c>
       <c r="D4" s="2">
-        <v>0.283637672662735</v>
+        <v>0.287142008543015</v>
       </c>
       <c r="E4" s="2">
-        <v>0.136773645877838</v>
+        <v>0.129752844572067</v>
       </c>
     </row>
     <row r="5">
@@ -2565,16 +2565,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="2">
-        <v>422990264892.578</v>
+        <v>411066528320.313</v>
       </c>
       <c r="C5" s="2">
-        <v>52762371063.2324</v>
+        <v>44105434417.7246</v>
       </c>
       <c r="D5" s="2">
-        <v>901211853027.344</v>
+        <v>935660339355.469</v>
       </c>
       <c r="E5" s="2">
-        <v>434575714111.328</v>
+        <v>422803283691.406</v>
       </c>
     </row>
     <row r="6">
@@ -2582,16 +2582,16 @@
         <v>24</v>
       </c>
       <c r="B6" s="2">
-        <v>0.00114513700827956</v>
+        <v>0.00113242061343044</v>
       </c>
       <c r="C6" s="2">
-        <v>1.68586393556325E-05</v>
+        <v>1.36408298203605E-05</v>
       </c>
       <c r="D6" s="2">
-        <v>0.00209612166509032</v>
+        <v>0.00207653385587037</v>
       </c>
       <c r="E6" s="2">
-        <v>0.00149230496026576</v>
+        <v>0.00147705792915076</v>
       </c>
     </row>
     <row r="7">
@@ -2599,16 +2599,16 @@
         <v>25</v>
       </c>
       <c r="B7" s="2">
-        <v>3638484.00115967</v>
+        <v>3690024.37591553</v>
       </c>
       <c r="C7" s="2">
-        <v>53565.5468702316</v>
+        <v>44449.0276277065</v>
       </c>
       <c r="D7" s="2">
-        <v>6660080.909729</v>
+        <v>6766443.72940063</v>
       </c>
       <c r="E7" s="2">
-        <v>4741552.82974243</v>
+        <v>4813034.53445435</v>
       </c>
     </row>
     <row r="8">
@@ -2616,16 +2616,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>5.71319833397865E-05</v>
+        <v>5.28580239915755E-05</v>
       </c>
       <c r="C8" s="2">
-        <v>1.68586393556325E-05</v>
+        <v>1.36408298203605E-05</v>
       </c>
       <c r="D8" s="2">
-        <v>0.000115776958409697</v>
+        <v>0.000114331676741131</v>
       </c>
       <c r="E8" s="2">
-        <v>5.71052732993849E-05</v>
+        <v>5.27761403645854E-05</v>
       </c>
     </row>
     <row r="9">
@@ -2633,16 +2633,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="2">
-        <v>0.431507389293984</v>
+        <v>0.473122578114271</v>
       </c>
       <c r="C9" s="2" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="D9" s="2">
-        <v>0.212489743717015</v>
+        <v>0.218073910218664</v>
       </c>
       <c r="E9" s="2">
-        <v>0.422860437538475</v>
+        <v>0.463814416434616</v>
       </c>
     </row>
     <row r="10">
@@ -2650,16 +2650,16 @@
         <v>28</v>
       </c>
       <c r="B10" s="2">
-        <v>0.817476570606232</v>
+        <v>0.805515170097351</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="2">
-        <v>0.808501720428467</v>
+        <v>0.795956909656525</v>
       </c>
       <c r="E10" s="2">
-        <v>0.81623512506485</v>
+        <v>0.803897738456726</v>
       </c>
     </row>
     <row r="11">
@@ -2667,16 +2667,16 @@
         <v>30</v>
       </c>
       <c r="B11" s="2">
-        <v>163.336637369792</v>
+        <v>153.639485677083</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="2">
-        <v>160.313037109375</v>
+        <v>150.677962239583</v>
       </c>
       <c r="E11" s="2">
-        <v>165.815185546875</v>
+        <v>155.902490234375</v>
       </c>
     </row>
     <row r="12">
@@ -2701,16 +2701,16 @@
         <v>32</v>
       </c>
       <c r="B13" s="2">
-        <v>120.564363606771</v>
+        <v>114.193627929687</v>
       </c>
       <c r="C13" s="2">
-        <v>-30.0737508138021</v>
+        <v>-30.5973063151042</v>
       </c>
       <c r="D13" s="2">
-        <v>119.490128580729</v>
+        <v>113.180607096354</v>
       </c>
       <c r="E13" s="2">
-        <v>122.900374348958</v>
+        <v>116.431819661458</v>
       </c>
     </row>
     <row r="14">
@@ -2718,16 +2718,16 @@
         <v>33</v>
       </c>
       <c r="B14" s="2">
-        <v>4503.3221244812</v>
+        <v>4676.71966552734</v>
       </c>
       <c r="C14" s="2" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="D14" s="2">
-        <v>2197.83854484558</v>
+        <v>2136.49320602417</v>
       </c>
       <c r="E14" s="2">
-        <v>4498.58617782593</v>
+        <v>4674.57056045532</v>
       </c>
     </row>
     <row r="15">
@@ -2735,16 +2735,16 @@
         <v>34</v>
       </c>
       <c r="B15" s="2">
-        <v>4228.85799407959</v>
+        <v>4361.41872406006</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="2">
-        <v>2043.89262199402</v>
+        <v>1971.5359210968</v>
       </c>
       <c r="E15" s="2">
-        <v>4207.00073242188</v>
+        <v>4338.58919143677</v>
       </c>
     </row>
   </sheetData>
